--- a/fix-bugs/ig/FRDeviceLMCDAFHIR.xlsx
+++ b/fix-bugs/ig/FRDeviceLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T11:41:07+00:00</t>
+    <t>2026-08-10T14:36:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-bugs/ig/FRDeviceLMCDAFHIR.xlsx
+++ b/fix-bugs/ig/FRDeviceLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T14:36:25+00:00</t>
+    <t>2026-08-10T19:10:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-bugs/ig/FRDeviceLMCDAFHIR.xlsx
+++ b/fix-bugs/ig/FRDeviceLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T19:10:11+00:00</t>
+    <t>2026-08-11T07:47:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
